--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodysitestatus.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodysitestatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-25</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodysitestatus.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodysitestatus.xlsx
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:CodeableConcept</t>
+    <t>element:Observation</t>
   </si>
   <si>
     <t>ID</t>
